--- a/data/trans_orig/Q5416-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2007</t>
+          <t>Población según si es capaz de moverse por su casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82327</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66267</t>
+          <t>66018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86761</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95002</t>
+          <t>94928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244003</t>
+          <t>244173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255381</t>
+          <t>255633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77559</t>
+          <t>78062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85752</t>
+          <t>84907</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324774</t>
+          <t>324714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>338855</t>
+          <t>338723</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47966</t>
+          <t>47861</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54647</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80597</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92839</t>
+          <t>92801</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>132914</t>
+          <t>132537</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>146258</t>
+          <t>146513</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>391792</t>
+          <t>391476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>411250</t>
+          <t>410516</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>394546</t>
+          <t>394532</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>413761</t>
+          <t>414426</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>42601</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>479334</t>
+          <t>478973</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>493561</t>
+          <t>493243</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>626662</t>
+          <t>625528</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>651232</t>
+          <t>649966</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1111205</t>
+          <t>1111526</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1139828</t>
+          <t>1139797</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2012</t>
+          <t>Población según si es capaz de moverse por su casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>62512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110143</t>
+          <t>110241</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117686</t>
+          <t>117691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49251</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163756</t>
+          <t>163741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172232</t>
+          <t>172209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,49 +6672,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>8</t>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204822</t>
+          <t>205503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222325</t>
+          <t>222444</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>54214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263305</t>
+          <t>263452</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281193</t>
+          <t>281280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28013</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>92103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101665</t>
+          <t>101603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>150061</t>
+          <t>151540</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>170199</t>
+          <t>170132</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>248580</t>
+          <t>247563</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>269209</t>
+          <t>269425</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25241</t>
+          <t>24097</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>350641</t>
+          <t>350160</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>373400</t>
+          <t>374323</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>352627</t>
+          <t>353175</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375539</t>
+          <t>375707</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>41229</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50839</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>47820</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>61581</t>
+          <t>63824</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>522543</t>
+          <t>523398</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>542765</t>
+          <t>543478</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>659421</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>688686</t>
+          <t>689823</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1189277</t>
+          <t>1188237</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1227327</t>
+          <t>1227046</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2016</t>
+          <t>Población según si es capaz de moverse por su casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95258</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51513</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60282</t>
+          <t>60864</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110968</t>
+          <t>110641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>119388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155458</t>
+          <t>154718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164889</t>
+          <t>164672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187231</t>
+          <t>187200</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198145</t>
+          <t>198878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83835</t>
+          <t>82319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96282</t>
+          <t>95587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275482</t>
+          <t>275369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291805</t>
+          <t>292020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133708</t>
+          <t>132529</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142811</t>
+          <t>142684</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>133704</t>
+          <t>132708</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>150723</t>
+          <t>150110</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>271384</t>
+          <t>271672</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>291210</t>
+          <t>291198</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>366323</t>
+          <t>366139</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>391267</t>
+          <t>390707</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>366323</t>
+          <t>366139</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>391267</t>
+          <t>390707</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>62243</t>
+          <t>59562</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>79841</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>555556</t>
+          <t>554846</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>573135</t>
+          <t>573479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>692037</t>
+          <t>696286</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>727141</t>
+          <t>728319</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1257957</t>
+          <t>1257581</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1296787</t>
+          <t>1296210</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2023</t>
+          <t>Población según si es capaz de moverse por su casa en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13399,12 +13399,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13512,12 +13512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13582,12 +13582,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13610,12 +13610,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13625,12 +13625,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13695,12 +13695,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13793,12 +13793,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91908</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>46535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136697</t>
+          <t>136687</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14572,12 +14572,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14650,12 +14650,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14720,12 +14720,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -14748,12 +14748,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92960</t>
+          <t>92632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100006</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14876,12 +14876,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14896,12 +14896,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142290</t>
+          <t>142807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150879</t>
+          <t>150674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15146,7 +15146,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15176,12 +15176,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15204,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>17212</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15387,12 +15387,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15402,12 +15402,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221298</t>
+          <t>221335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232124</t>
+          <t>232102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>307303</t>
+          <t>307288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>325740</t>
+          <t>325717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>535662</t>
+          <t>534645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559304</t>
+          <t>558465</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15515,12 +15515,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15695,12 +15695,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15730,12 +15730,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15858,12 +15858,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -15886,97 +15886,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1184</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4177</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1184</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4160</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1184</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3889</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87462</t>
+          <t>87096</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91535</t>
+          <t>91506</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16014,12 +16014,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>174828</t>
+          <t>175156</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>187793</t>
+          <t>187531</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16049,12 +16049,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16069,12 +16069,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>264619</t>
+          <t>264689</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>278312</t>
+          <t>277997</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16084,12 +16084,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -16229,12 +16229,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16357,12 +16357,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16377,12 +16377,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16470,12 +16470,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -16568,12 +16568,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16583,12 +16583,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>277383</t>
+          <t>277862</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>293755</t>
+          <t>295071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>281054</t>
+          <t>280079</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>298359</t>
+          <t>297440</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16833,12 +16833,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>27486</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16883,12 +16883,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24025</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>60902</t>
+          <t>59926</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>68998</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17059,12 +17059,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17074,12 +17074,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -17137,12 +17137,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>611542</t>
+          <t>612139</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>626092</t>
+          <t>625705</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>927887</t>
+          <t>928627</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>984210</t>
+          <t>982807</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17187,12 +17187,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1551262</t>
+          <t>1552532</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1600614</t>
+          <t>1601807</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5416-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Clase-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82901</t>
+          <t>84039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>66159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87068</t>
+          <t>86570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94928</t>
+          <t>95013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>244173</t>
+          <t>243095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255633</t>
+          <t>255425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78062</t>
+          <t>78260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84907</t>
+          <t>84911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324714</t>
+          <t>325309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>338723</t>
+          <t>339036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54628</t>
+          <t>54640</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81742</t>
+          <t>81275</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92801</t>
+          <t>92887</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>132537</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>146513</t>
+          <t>146612</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>391476</t>
+          <t>391777</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>410516</t>
+          <t>410959</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>394532</t>
+          <t>395061</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>414426</t>
+          <t>414320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>44729</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>478973</t>
+          <t>479813</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>493243</t>
+          <t>493247</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>625528</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>649966</t>
+          <t>649874</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1111526</t>
+          <t>1112555</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1139797</t>
+          <t>1139878</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>68068</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77419</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110241</t>
+          <t>109789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117691</t>
+          <t>117689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>49224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163741</t>
+          <t>163733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172209</t>
+          <t>172216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205503</t>
+          <t>206105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222444</t>
+          <t>221905</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263452</t>
+          <t>263358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281280</t>
+          <t>281240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>92103</t>
+          <t>93116</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101603</t>
+          <t>101664</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>151540</t>
+          <t>149898</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>170132</t>
+          <t>169678</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>247563</t>
+          <t>248999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>269425</t>
+          <t>269566</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24764</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>146</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>350160</t>
+          <t>351644</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>374323</t>
+          <t>373556</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>353175</t>
+          <t>353560</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>375707</t>
+          <t>375878</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>39631</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50794</t>
+          <t>49974</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>47462</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>35397</t>
+          <t>35132</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>63824</t>
+          <t>63061</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>523398</t>
+          <t>521963</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>543478</t>
+          <t>543602</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>659421</t>
+          <t>658469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>689823</t>
+          <t>690705</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1188237</t>
+          <t>1189209</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1227046</t>
+          <t>1226701</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96556</t>
+          <t>95336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>60495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69162</t>
+          <t>69064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>778</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>110911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119388</t>
+          <t>119376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>40650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154718</t>
+          <t>156173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164672</t>
+          <t>164809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187200</t>
+          <t>187076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198878</t>
+          <t>198175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82319</t>
+          <t>83752</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95587</t>
+          <t>95427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275369</t>
+          <t>275297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>292020</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>132529</t>
+          <t>133918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142684</t>
+          <t>142761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>132708</t>
+          <t>134465</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>150110</t>
+          <t>151197</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>271672</t>
+          <t>271260</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>291198</t>
+          <t>290857</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12082,12 +12082,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>366139</t>
+          <t>366851</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>390707</t>
+          <t>392041</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>366139</t>
+          <t>366851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>390707</t>
+          <t>392041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>23587</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>31241</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>46494</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>79841</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>554846</t>
+          <t>554171</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>573479</t>
+          <t>573445</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>696286</t>
+          <t>692896</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>728319</t>
+          <t>728280</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1257581</t>
+          <t>1257902</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1296210</t>
+          <t>1294958</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>581</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -14287,27 +14287,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>104117</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91928</t>
+          <t>101139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>51002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>139784</t>
+          <t>157866</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136687</t>
+          <t>154409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141354</t>
+          <t>159504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -14630,102 +14630,102 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6154</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>10,62%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>6479</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>11688</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>5976</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>10739</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>657</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -14823,12 +14823,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97237</t>
+          <t>107470</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92632</t>
+          <t>102960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99857</t>
+          <t>110123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,32 +14891,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50292</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>51042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52002</t>
+          <t>56899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>147529</t>
+          <t>162485</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142807</t>
+          <t>156998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150674</t>
+          <t>166337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,32 +15086,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15121,32 +15121,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15156,32 +15156,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,32 +15234,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -15312,22 +15312,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>227397</t>
+          <t>247845</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221335</t>
+          <t>240050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232102</t>
+          <t>252648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>320434</t>
+          <t>124375</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>307288</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>325717</t>
+          <t>127428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>547831</t>
+          <t>372219</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>534645</t>
+          <t>364375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>558465</t>
+          <t>378117</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -15665,12 +15665,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,32 +15725,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>895</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -15778,12 +15778,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>90160</t>
+          <t>98947</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87096</t>
+          <t>95896</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>91506</t>
+          <t>100198</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>181842</t>
+          <t>194666</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175156</t>
+          <t>187285</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>187531</t>
+          <t>201429</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>272003</t>
+          <t>293613</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>264689</t>
+          <t>285800</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>277997</t>
+          <t>300153</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16259,32 +16259,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16294,22 +16294,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -16485,67 +16485,67 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>4309</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>8841</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -16598,32 +16598,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>286803</t>
+          <t>307670</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>277862</t>
+          <t>297223</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>295071</t>
+          <t>316306</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16633,32 +16633,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>290007</t>
+          <t>310946</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>280079</t>
+          <t>300580</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>297440</t>
+          <t>319812</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -16906,32 +16906,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>59926</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>75131</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -17019,17 +17019,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>619964</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>612139</t>
+          <t>673361</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>625705</t>
+          <t>688567</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>950090</t>
+          <t>810033</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>928627</t>
+          <t>797556</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>982807</t>
+          <t>822409</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1570054</t>
+          <t>1492090</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1552532</t>
+          <t>1476749</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1601807</t>
+          <t>1505558</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
